--- a/docs/Salary Calculations.xlsx
+++ b/docs/Salary Calculations.xlsx
@@ -1,19 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\projects\hrportal\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\projects\hrportal\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1A4D1E43-CA82-4017-BF71-6B842CD5FB37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0D25B39-C9C2-49EC-95D3-2C21E4D7100C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="29020" windowHeight="17500" xr2:uid="{461494F0-5780-47EA-B1B9-BB98E395037F}"/>
+    <workbookView xWindow="47910" yWindow="0" windowWidth="19380" windowHeight="10530" xr2:uid="{461494F0-5780-47EA-B1B9-BB98E395037F}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -34,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="287" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="288" uniqueCount="60">
   <si>
     <t>layla</t>
   </si>
@@ -211,6 +212,9 @@
   </si>
   <si>
     <t>Net Transaction Pay</t>
+  </si>
+  <si>
+    <t>wd</t>
   </si>
 </sst>
 </file>
@@ -596,36 +600,36 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{068B6A2D-3AC9-4114-8B39-1D0D1002F4FE}">
   <dimension ref="B2:X59"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="3" customWidth="1"/>
-    <col min="2" max="2" width="19.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.796875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="48" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="3.6328125" customWidth="1"/>
-    <col min="6" max="6" width="19.81640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="43.7265625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="3.90625" customWidth="1"/>
-    <col min="10" max="10" width="19.90625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="15.36328125" customWidth="1"/>
-    <col min="12" max="12" width="43.7265625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="3.81640625" customWidth="1"/>
-    <col min="14" max="14" width="19.90625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="11.7265625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="43.7265625" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="4.36328125" customWidth="1"/>
-    <col min="18" max="18" width="19.90625" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="43.7265625" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="4.08984375" customWidth="1"/>
-    <col min="22" max="22" width="19.90625" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="12.36328125" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="43.7265625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="3.59765625" customWidth="1"/>
+    <col min="6" max="6" width="19.796875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="43.73046875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="3.9296875" customWidth="1"/>
+    <col min="10" max="10" width="19.9296875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="15.33203125" customWidth="1"/>
+    <col min="12" max="12" width="43.73046875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="3.796875" customWidth="1"/>
+    <col min="14" max="14" width="19.9296875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="11.73046875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="43.73046875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="4.33203125" customWidth="1"/>
+    <col min="18" max="18" width="19.9296875" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="43.73046875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="4.06640625" customWidth="1"/>
+    <col min="22" max="22" width="19.9296875" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="43.73046875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:24" x14ac:dyDescent="0.35">
+    <row r="2" spans="2:24" x14ac:dyDescent="0.45">
       <c r="H2" s="3"/>
       <c r="L2" s="8"/>
     </row>
-    <row r="4" spans="2:24" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B4" s="7" t="s">
         <v>52</v>
       </c>
@@ -682,7 +686,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="5" spans="2:24" x14ac:dyDescent="0.35">
+    <row r="5" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B5" s="1" t="s">
         <v>12</v>
       </c>
@@ -720,7 +724,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="6" spans="2:24" x14ac:dyDescent="0.35">
+    <row r="6" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B6" s="1" t="s">
         <v>15</v>
       </c>
@@ -758,7 +762,7 @@
         <v>46081</v>
       </c>
     </row>
-    <row r="7" spans="2:24" x14ac:dyDescent="0.35">
+    <row r="7" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B7" t="s">
         <v>5</v>
       </c>
@@ -815,7 +819,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="8" spans="2:24" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B8" t="s">
         <v>6</v>
       </c>
@@ -872,7 +876,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="9" spans="2:24" x14ac:dyDescent="0.35">
+    <row r="9" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B9" s="7" t="s">
         <v>28</v>
       </c>
@@ -929,7 +933,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="10" spans="2:24" x14ac:dyDescent="0.35">
+    <row r="10" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B10" t="s">
         <v>11</v>
       </c>
@@ -992,7 +996,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="11" spans="2:24" x14ac:dyDescent="0.35">
+    <row r="11" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B11" t="s">
         <v>19</v>
       </c>
@@ -1055,7 +1059,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="12" spans="2:24" x14ac:dyDescent="0.35">
+    <row r="12" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B12" t="s">
         <v>14</v>
       </c>
@@ -1118,7 +1122,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="13" spans="2:24" x14ac:dyDescent="0.35">
+    <row r="13" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B13" t="s">
         <v>7</v>
       </c>
@@ -1156,7 +1160,7 @@
         <v>1800</v>
       </c>
     </row>
-    <row r="14" spans="2:24" x14ac:dyDescent="0.35">
+    <row r="14" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B14" t="s">
         <v>8</v>
       </c>
@@ -1213,7 +1217,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="15" spans="2:24" x14ac:dyDescent="0.35">
+    <row r="15" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B15" t="s">
         <v>9</v>
       </c>
@@ -1257,7 +1261,7 @@
         <v>69.230769230769226</v>
       </c>
     </row>
-    <row r="16" spans="2:24" x14ac:dyDescent="0.35">
+    <row r="16" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B16" t="s">
         <v>10</v>
       </c>
@@ -1301,7 +1305,7 @@
         <v>11.538461538461538</v>
       </c>
     </row>
-    <row r="17" spans="2:24" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B17" t="s">
         <v>17</v>
       </c>
@@ -1363,7 +1367,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="18" spans="2:24" x14ac:dyDescent="0.35">
+    <row r="18" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B18" t="s">
         <v>18</v>
       </c>
@@ -1425,7 +1429,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="19" spans="2:24" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B19" t="s">
         <v>20</v>
       </c>
@@ -1487,7 +1491,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="20" spans="2:24" x14ac:dyDescent="0.35">
+    <row r="20" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B20" t="s">
         <v>21</v>
       </c>
@@ -1549,7 +1553,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="21" spans="2:24" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B21" t="s">
         <v>22</v>
       </c>
@@ -1611,7 +1615,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="22" spans="2:24" s="2" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="2:24" s="2" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B22" s="2" t="s">
         <v>56</v>
       </c>
@@ -1673,7 +1677,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="23" spans="2:24" x14ac:dyDescent="0.35">
+    <row r="23" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B23" s="6" t="s">
         <v>57</v>
       </c>
@@ -1717,7 +1721,7 @@
         <v>484.61538461538464</v>
       </c>
     </row>
-    <row r="24" spans="2:24" x14ac:dyDescent="0.35">
+    <row r="24" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B24" s="6" t="s">
         <v>24</v>
       </c>
@@ -1761,7 +1765,7 @@
         <v>346.15384615384613</v>
       </c>
     </row>
-    <row r="25" spans="2:24" x14ac:dyDescent="0.35">
+    <row r="25" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B25" s="6" t="s">
         <v>35</v>
       </c>
@@ -1805,7 +1809,7 @@
         <v>57.692307692307693</v>
       </c>
     </row>
-    <row r="26" spans="2:24" s="2" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="2:24" s="2" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B26" s="9" t="s">
         <v>55</v>
       </c>
@@ -1849,7 +1853,7 @@
         <v>1050</v>
       </c>
     </row>
-    <row r="27" spans="2:24" x14ac:dyDescent="0.35">
+    <row r="27" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B27" s="6" t="s">
         <v>25</v>
       </c>
@@ -1893,7 +1897,7 @@
         <v>1050</v>
       </c>
     </row>
-    <row r="28" spans="2:24" x14ac:dyDescent="0.35">
+    <row r="28" spans="2:24" x14ac:dyDescent="0.45">
       <c r="B28" s="6" t="s">
         <v>22</v>
       </c>
@@ -1937,7 +1941,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="2:24" s="2" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="2:24" s="2" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B29" s="9" t="s">
         <v>58</v>
       </c>
@@ -1981,20 +1985,24 @@
         <v>1938.4615384615386</v>
       </c>
     </row>
-    <row r="30" spans="2:24" x14ac:dyDescent="0.35">
+    <row r="30" spans="2:24" x14ac:dyDescent="0.45">
+      <c r="C30">
+        <f>C29+1158.371</f>
+        <v>4261.1402307692306</v>
+      </c>
       <c r="F30" s="3"/>
       <c r="G30" s="3"/>
     </row>
-    <row r="31" spans="2:24" x14ac:dyDescent="0.35">
+    <row r="31" spans="2:24" x14ac:dyDescent="0.45">
       <c r="F31" s="3"/>
       <c r="G31" s="3"/>
       <c r="V31" s="6"/>
     </row>
-    <row r="32" spans="2:24" x14ac:dyDescent="0.35">
+    <row r="32" spans="2:24" x14ac:dyDescent="0.45">
       <c r="O32" s="4"/>
       <c r="V32" s="6"/>
     </row>
-    <row r="34" spans="6:10" x14ac:dyDescent="0.35">
+    <row r="34" spans="6:10" x14ac:dyDescent="0.45">
       <c r="F34" s="2" t="s">
         <v>52</v>
       </c>
@@ -2005,7 +2013,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="35" spans="6:10" x14ac:dyDescent="0.35">
+    <row r="35" spans="6:10" x14ac:dyDescent="0.45">
       <c r="F35" t="s">
         <v>13</v>
       </c>
@@ -2013,7 +2021,7 @@
         <v>46054</v>
       </c>
     </row>
-    <row r="36" spans="6:10" x14ac:dyDescent="0.35">
+    <row r="36" spans="6:10" x14ac:dyDescent="0.45">
       <c r="F36" t="s">
         <v>26</v>
       </c>
@@ -2021,7 +2029,7 @@
         <v>46081</v>
       </c>
     </row>
-    <row r="37" spans="6:10" x14ac:dyDescent="0.35">
+    <row r="37" spans="6:10" x14ac:dyDescent="0.45">
       <c r="F37" t="s">
         <v>5</v>
       </c>
@@ -2032,7 +2040,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="38" spans="6:10" x14ac:dyDescent="0.35">
+    <row r="38" spans="6:10" x14ac:dyDescent="0.45">
       <c r="F38" t="s">
         <v>6</v>
       </c>
@@ -2043,7 +2051,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="39" spans="6:10" x14ac:dyDescent="0.35">
+    <row r="39" spans="6:10" x14ac:dyDescent="0.45">
       <c r="F39" s="3" t="s">
         <v>28</v>
       </c>
@@ -2054,7 +2062,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="40" spans="6:10" x14ac:dyDescent="0.35">
+    <row r="40" spans="6:10" x14ac:dyDescent="0.45">
       <c r="F40" t="s">
         <v>11</v>
       </c>
@@ -2066,7 +2074,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="41" spans="6:10" x14ac:dyDescent="0.35">
+    <row r="41" spans="6:10" x14ac:dyDescent="0.45">
       <c r="F41" t="s">
         <v>19</v>
       </c>
@@ -2078,7 +2086,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="42" spans="6:10" x14ac:dyDescent="0.35">
+    <row r="42" spans="6:10" x14ac:dyDescent="0.45">
       <c r="F42" t="s">
         <v>14</v>
       </c>
@@ -2094,7 +2102,7 @@
         <v>4041.3461538461543</v>
       </c>
     </row>
-    <row r="43" spans="6:10" x14ac:dyDescent="0.35">
+    <row r="43" spans="6:10" x14ac:dyDescent="0.45">
       <c r="F43" t="s">
         <v>7</v>
       </c>
@@ -2102,7 +2110,7 @@
         <v>7500</v>
       </c>
     </row>
-    <row r="44" spans="6:10" x14ac:dyDescent="0.35">
+    <row r="44" spans="6:10" x14ac:dyDescent="0.45">
       <c r="F44" t="s">
         <v>8</v>
       </c>
@@ -2113,7 +2121,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="45" spans="6:10" x14ac:dyDescent="0.35">
+    <row r="45" spans="6:10" x14ac:dyDescent="0.45">
       <c r="F45" t="s">
         <v>9</v>
       </c>
@@ -2126,7 +2134,7 @@
         <v>326.92307692307691</v>
       </c>
     </row>
-    <row r="46" spans="6:10" x14ac:dyDescent="0.35">
+    <row r="46" spans="6:10" x14ac:dyDescent="0.45">
       <c r="F46" t="s">
         <v>10</v>
       </c>
@@ -2135,7 +2143,7 @@
         <v>38.46153846153846</v>
       </c>
     </row>
-    <row r="47" spans="6:10" x14ac:dyDescent="0.35">
+    <row r="47" spans="6:10" x14ac:dyDescent="0.45">
       <c r="F47" t="s">
         <v>17</v>
       </c>
@@ -2147,7 +2155,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="48" spans="6:10" x14ac:dyDescent="0.35">
+    <row r="48" spans="6:10" x14ac:dyDescent="0.45">
       <c r="F48" t="s">
         <v>18</v>
       </c>
@@ -2159,7 +2167,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="49" spans="6:8" x14ac:dyDescent="0.35">
+    <row r="49" spans="6:8" x14ac:dyDescent="0.45">
       <c r="F49" t="s">
         <v>20</v>
       </c>
@@ -2171,7 +2179,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="50" spans="6:8" x14ac:dyDescent="0.35">
+    <row r="50" spans="6:8" x14ac:dyDescent="0.45">
       <c r="F50" t="s">
         <v>21</v>
       </c>
@@ -2183,7 +2191,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="51" spans="6:8" x14ac:dyDescent="0.35">
+    <row r="51" spans="6:8" x14ac:dyDescent="0.45">
       <c r="F51" t="s">
         <v>22</v>
       </c>
@@ -2195,7 +2203,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="52" spans="6:8" x14ac:dyDescent="0.35">
+    <row r="52" spans="6:8" x14ac:dyDescent="0.45">
       <c r="F52" s="2" t="s">
         <v>56</v>
       </c>
@@ -2207,7 +2215,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="53" spans="6:8" x14ac:dyDescent="0.35">
+    <row r="53" spans="6:8" x14ac:dyDescent="0.45">
       <c r="F53" s="6" t="s">
         <v>57</v>
       </c>
@@ -2216,7 +2224,7 @@
         <v>5884.6153846153848</v>
       </c>
     </row>
-    <row r="54" spans="6:8" x14ac:dyDescent="0.35">
+    <row r="54" spans="6:8" x14ac:dyDescent="0.45">
       <c r="F54" s="6" t="s">
         <v>24</v>
       </c>
@@ -2225,7 +2233,7 @@
         <v>5192.3076923076924</v>
       </c>
     </row>
-    <row r="55" spans="6:8" x14ac:dyDescent="0.35">
+    <row r="55" spans="6:8" x14ac:dyDescent="0.45">
       <c r="F55" s="6" t="s">
         <v>35</v>
       </c>
@@ -2234,7 +2242,7 @@
         <v>692.30769230769226</v>
       </c>
     </row>
-    <row r="56" spans="6:8" x14ac:dyDescent="0.35">
+    <row r="56" spans="6:8" x14ac:dyDescent="0.45">
       <c r="F56" s="9" t="s">
         <v>55</v>
       </c>
@@ -2244,7 +2252,7 @@
       </c>
       <c r="H56" s="2"/>
     </row>
-    <row r="57" spans="6:8" x14ac:dyDescent="0.35">
+    <row r="57" spans="6:8" x14ac:dyDescent="0.45">
       <c r="F57" s="6" t="s">
         <v>25</v>
       </c>
@@ -2253,7 +2261,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="6:8" x14ac:dyDescent="0.35">
+    <row r="58" spans="6:8" x14ac:dyDescent="0.45">
       <c r="F58" s="6" t="s">
         <v>22</v>
       </c>
@@ -2262,7 +2270,7 @@
         <v>-862.5</v>
       </c>
     </row>
-    <row r="59" spans="6:8" x14ac:dyDescent="0.35">
+    <row r="59" spans="6:8" x14ac:dyDescent="0.45">
       <c r="F59" s="9" t="s">
         <v>58</v>
       </c>
@@ -2271,6 +2279,118 @@
         <v>10906.73076923077</v>
       </c>
       <c r="H59" s="2"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{613003AF-99E8-4755-82B3-8F369EFACA3A}">
+  <dimension ref="B8:I19"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetData>
+    <row r="8" spans="2:9" x14ac:dyDescent="0.45">
+      <c r="B8">
+        <v>3500</v>
+      </c>
+      <c r="C8">
+        <v>7500</v>
+      </c>
+      <c r="D8">
+        <v>2400</v>
+      </c>
+      <c r="E8">
+        <v>2200</v>
+      </c>
+      <c r="F8">
+        <v>1800</v>
+      </c>
+      <c r="G8">
+        <v>1500</v>
+      </c>
+      <c r="H8">
+        <v>3200</v>
+      </c>
+    </row>
+    <row r="9" spans="2:9" x14ac:dyDescent="0.45">
+      <c r="B9">
+        <v>1266.9680000000001</v>
+      </c>
+      <c r="C9">
+        <v>2714.9319999999998</v>
+      </c>
+      <c r="D9">
+        <v>868.77800000000002</v>
+      </c>
+      <c r="E9">
+        <v>796.38</v>
+      </c>
+      <c r="F9">
+        <v>651.58399999999995</v>
+      </c>
+      <c r="G9">
+        <v>542.98599999999999</v>
+      </c>
+      <c r="H9">
+        <v>1158.3710000000001</v>
+      </c>
+    </row>
+    <row r="10" spans="2:9" x14ac:dyDescent="0.45">
+      <c r="B10">
+        <f>B9/B8</f>
+        <v>0.36199085714285717</v>
+      </c>
+      <c r="C10">
+        <f>C9/C8</f>
+        <v>0.36199093333333332</v>
+      </c>
+      <c r="D10">
+        <f>D9/D8</f>
+        <v>0.36199083333333332</v>
+      </c>
+      <c r="E10">
+        <f>E9/E8</f>
+        <v>0.36199090909090909</v>
+      </c>
+      <c r="F10">
+        <f>F9/F8</f>
+        <v>0.3619911111111111</v>
+      </c>
+      <c r="G10">
+        <f>G9/G8</f>
+        <v>0.36199066666666668</v>
+      </c>
+      <c r="H10">
+        <f>H9/H8</f>
+        <v>0.36199093750000005</v>
+      </c>
+    </row>
+    <row r="16" spans="2:9" x14ac:dyDescent="0.45">
+      <c r="H16">
+        <v>24</v>
+      </c>
+      <c r="I16" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="17" spans="8:8" x14ac:dyDescent="0.45">
+      <c r="H17">
+        <f>1500*24/26</f>
+        <v>1384.6153846153845</v>
+      </c>
+    </row>
+    <row r="18" spans="8:8" x14ac:dyDescent="0.45">
+      <c r="H18">
+        <f>100*24/26</f>
+        <v>92.307692307692307</v>
+      </c>
+    </row>
+    <row r="19" spans="8:8" x14ac:dyDescent="0.45">
+      <c r="H19">
+        <f>70*24/26</f>
+        <v>64.615384615384613</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
